--- a/output/Chp2_tables/Chapter 2 - Table 3.xlsx
+++ b/output/Chp2_tables/Chapter 2 - Table 3.xlsx
@@ -88,355 +88,355 @@
     <t>POCVL, pre-treatment DR testing and DR testing at failure at 3 times ACT-UP level</t>
   </si>
   <si>
-    <t>45,421 (27,657-85,776)</t>
-  </si>
-  <si>
-    <t>44,657 (27,181-84,934)</t>
-  </si>
-  <si>
-    <t>44,277 (26,843-84,263)</t>
-  </si>
-  <si>
-    <t>43,957 (26,591-83,738)</t>
-  </si>
-  <si>
-    <t>44,644 (27,169-84,906)</t>
-  </si>
-  <si>
-    <t>44,115 (26,782-84,131)</t>
-  </si>
-  <si>
-    <t>43,648 (26,424-83,528)</t>
-  </si>
-  <si>
-    <t>43,702 (25,965-83,983)</t>
-  </si>
-  <si>
-    <t>42,438 (25,179-82,765)</t>
-  </si>
-  <si>
-    <t>41,394 (24,223-81,474)</t>
-  </si>
-  <si>
-    <t>43,619 (25,904-83,932)</t>
-  </si>
-  <si>
-    <t>42,280 (25,167-82,740)</t>
-  </si>
-  <si>
-    <t>41,232 (24,108-81,340)</t>
-  </si>
-  <si>
-    <t>11,898 (4,066-31,839)</t>
-  </si>
-  <si>
-    <t>11,698 (3,957-31,571)</t>
-  </si>
-  <si>
-    <t>11,518 (3,891-31,157)</t>
-  </si>
-  <si>
-    <t>11,401 (3,840-30,758)</t>
-  </si>
-  <si>
-    <t>11,612 (3,938-31,369)</t>
-  </si>
-  <si>
-    <t>11,340 (3,866-30,654)</t>
-  </si>
-  <si>
-    <t>11,127 (3,791-30,122)</t>
-  </si>
-  <si>
-    <t>10,634 (3,508-28,876)</t>
-  </si>
-  <si>
-    <t>9,676 (3,085-26,787)</t>
-  </si>
-  <si>
-    <t>8,955 (2,764-25,578)</t>
-  </si>
-  <si>
-    <t>10,576 (3,494-28,810)</t>
-  </si>
-  <si>
-    <t>9,606 (3,071-26,657)</t>
-  </si>
-  <si>
-    <t>8,857 (2,733-25,197)</t>
-  </si>
-  <si>
-    <t>2,249 (889-5,302)</t>
-  </si>
-  <si>
-    <t>2,100 (827-5,097)</t>
-  </si>
-  <si>
-    <t>2,016 (777-4,960)</t>
-  </si>
-  <si>
-    <t>1,930 (742-4,895)</t>
-  </si>
-  <si>
-    <t>1,881 (733-4,452)</t>
-  </si>
-  <si>
-    <t>1,547 (607-3,633)</t>
-  </si>
-  <si>
-    <t>1,248 (490-2,825)</t>
-  </si>
-  <si>
-    <t>2,082 (816-5,051)</t>
-  </si>
-  <si>
-    <t>1,977 (768-4,871)</t>
-  </si>
-  <si>
-    <t>1,886 (730-4,768)</t>
-  </si>
-  <si>
-    <t>1,864 (728-4,413)</t>
-  </si>
-  <si>
-    <t>1,527 (597-3,553)</t>
-  </si>
-  <si>
-    <t>1,226 (482-2,733)</t>
-  </si>
-  <si>
-    <t>5,644 (2,092-14,430)</t>
-  </si>
-  <si>
-    <t>5,589 (2,067-14,307)</t>
-  </si>
-  <si>
-    <t>5,548 (2,047-14,216)</t>
-  </si>
-  <si>
-    <t>5,516 (2,030-14,146)</t>
-  </si>
-  <si>
-    <t>4,466 (1,654-11,427)</t>
-  </si>
-  <si>
-    <t>3,321 (1,228-8,497)</t>
-  </si>
-  <si>
-    <t>2,194 (810-5,622)</t>
-  </si>
-  <si>
-    <t>5,422 (1,992-13,752)</t>
-  </si>
-  <si>
-    <t>5,224 (1,907-13,202)</t>
-  </si>
-  <si>
-    <t>5,052 (1,835-12,750)</t>
-  </si>
-  <si>
-    <t>4,334 (1,592-10,986)</t>
-  </si>
-  <si>
-    <t>3,130 (1,143-7,886)</t>
-  </si>
-  <si>
-    <t>2,018 (733-5,034)</t>
+    <t>62,609 (41,125-101,988)</t>
+  </si>
+  <si>
+    <t>61,871 (40,618-101,567)</t>
+  </si>
+  <si>
+    <t>61,360 (40,275-100,944)</t>
+  </si>
+  <si>
+    <t>60,989 (40,029-100,261)</t>
+  </si>
+  <si>
+    <t>61,822 (40,561-101,558)</t>
+  </si>
+  <si>
+    <t>61,271 (40,213-100,716)</t>
+  </si>
+  <si>
+    <t>60,801 (39,818-99,932)</t>
+  </si>
+  <si>
+    <t>60,761 (39,684-99,934)</t>
+  </si>
+  <si>
+    <t>59,536 (38,478-97,937)</t>
+  </si>
+  <si>
+    <t>58,506 (37,620-96,560)</t>
+  </si>
+  <si>
+    <t>60,714 (39,645-99,898)</t>
+  </si>
+  <si>
+    <t>59,457 (38,421-97,891)</t>
+  </si>
+  <si>
+    <t>58,418 (37,542-96,391)</t>
+  </si>
+  <si>
+    <t>12,995 (5,614-27,840)</t>
+  </si>
+  <si>
+    <t>12,757 (5,450-27,391)</t>
+  </si>
+  <si>
+    <t>12,546 (5,351-27,065)</t>
+  </si>
+  <si>
+    <t>12,394 (5,279-26,832)</t>
+  </si>
+  <si>
+    <t>12,699 (5,435-27,321)</t>
+  </si>
+  <si>
+    <t>12,430 (5,317-26,895)</t>
+  </si>
+  <si>
+    <t>12,223 (5,224-26,492)</t>
+  </si>
+  <si>
+    <t>11,654 (4,910-25,889)</t>
+  </si>
+  <si>
+    <t>10,645 (4,453-24,411)</t>
+  </si>
+  <si>
+    <t>9,926 (4,027-23,304)</t>
+  </si>
+  <si>
+    <t>11,622 (4,904-25,801)</t>
+  </si>
+  <si>
+    <t>10,585 (4,448-24,245)</t>
+  </si>
+  <si>
+    <t>9,856 (3,960-23,067)</t>
+  </si>
+  <si>
+    <t>2,044 (890-4,161)</t>
+  </si>
+  <si>
+    <t>1,883 (815-3,826)</t>
+  </si>
+  <si>
+    <t>1,769 (758-3,608)</t>
+  </si>
+  <si>
+    <t>1,670 (717-3,446)</t>
+  </si>
+  <si>
+    <t>1,700 (737-3,481)</t>
+  </si>
+  <si>
+    <t>1,412 (604-2,909)</t>
+  </si>
+  <si>
+    <t>1,145 (487-2,408)</t>
+  </si>
+  <si>
+    <t>1,870 (811-3,809)</t>
+  </si>
+  <si>
+    <t>1,752 (750-3,577)</t>
+  </si>
+  <si>
+    <t>1,643 (707-3,394)</t>
+  </si>
+  <si>
+    <t>1,689 (732-3,462)</t>
+  </si>
+  <si>
+    <t>1,398 (597-2,885)</t>
+  </si>
+  <si>
+    <t>1,135 (483-2,389)</t>
+  </si>
+  <si>
+    <t>4,582 (2,035-9,276)</t>
+  </si>
+  <si>
+    <t>4,547 (2,015-9,199)</t>
+  </si>
+  <si>
+    <t>4,512 (1,998-9,136)</t>
+  </si>
+  <si>
+    <t>4,487 (1,984-9,087)</t>
+  </si>
+  <si>
+    <t>3,636 (1,612-7,349)</t>
+  </si>
+  <si>
+    <t>2,704 (1,198-5,468)</t>
+  </si>
+  <si>
+    <t>1,791 (793-3,622)</t>
+  </si>
+  <si>
+    <t>4,436 (1,970-8,938)</t>
+  </si>
+  <si>
+    <t>4,303 (1,911-8,684)</t>
+  </si>
+  <si>
+    <t>4,190 (1,862-8,538)</t>
+  </si>
+  <si>
+    <t>3,548 (1,575-7,140)</t>
+  </si>
+  <si>
+    <t>2,579 (1,146-5,199)</t>
+  </si>
+  <si>
+    <t>1,672 (744-3,404)</t>
   </si>
   <si>
     <t>0.0 (0.0-0.0)</t>
   </si>
   <si>
-    <t>20,076 (15,747-25,198)</t>
-  </si>
-  <si>
-    <t>39,937 (31,278-50,173)</t>
-  </si>
-  <si>
-    <t>59,664 (46,649-75,009)</t>
-  </si>
-  <si>
-    <t>20,062 (15,750-25,106)</t>
-  </si>
-  <si>
-    <t>39,865 (31,248-49,785)</t>
-  </si>
-  <si>
-    <t>59,482 (46,575-74,103)</t>
-  </si>
-  <si>
-    <t>19,750 (15,532-24,547)</t>
-  </si>
-  <si>
-    <t>38,844 (30,640-48,219)</t>
-  </si>
-  <si>
-    <t>57,568 (45,383-71,018)</t>
-  </si>
-  <si>
-    <t>19,737 (15,535-24,546)</t>
-  </si>
-  <si>
-    <t>38,783 (30,650-48,110)</t>
-  </si>
-  <si>
-    <t>57,419 (45,303-70,875)</t>
-  </si>
-  <si>
-    <t>4,977 (3,552-7,782)</t>
-  </si>
-  <si>
-    <t>9,904 (7,061-15,527)</t>
-  </si>
-  <si>
-    <t>14,800 (10,569-23,237)</t>
-  </si>
-  <si>
-    <t>3,189 (1,841-5,287)</t>
-  </si>
-  <si>
-    <t>3,423 (1,913-5,797)</t>
-  </si>
-  <si>
-    <t>3,501 (1,902-6,114)</t>
-  </si>
-  <si>
-    <t>8,192 (5,972-11,853)</t>
-  </si>
-  <si>
-    <t>13,191 (9,691-19,212)</t>
-  </si>
-  <si>
-    <t>17,897 (13,078-26,514)</t>
+    <t>20,910 (16,893-25,600)</t>
+  </si>
+  <si>
+    <t>41,605 (33,591-50,968)</t>
+  </si>
+  <si>
+    <t>62,159 (50,258-76,222)</t>
+  </si>
+  <si>
+    <t>20,897 (16,879-25,558)</t>
+  </si>
+  <si>
+    <t>41,558 (33,564-50,815)</t>
+  </si>
+  <si>
+    <t>62,071 (50,233-75,946)</t>
+  </si>
+  <si>
+    <t>20,646 (16,723-25,220)</t>
+  </si>
+  <si>
+    <t>40,660 (32,995-49,719)</t>
+  </si>
+  <si>
+    <t>60,347 (49,038-73,593)</t>
+  </si>
+  <si>
+    <t>20,636 (16,716-25,201)</t>
+  </si>
+  <si>
+    <t>40,639 (32,979-49,688)</t>
+  </si>
+  <si>
+    <t>60,279 (48,973-73,346)</t>
+  </si>
+  <si>
+    <t>5,470 (4,190-7,753)</t>
+  </si>
+  <si>
+    <t>10,900 (8,350-15,431)</t>
+  </si>
+  <si>
+    <t>16,282 (12,493-23,052)</t>
+  </si>
+  <si>
+    <t>3,171 (1,871-5,190)</t>
+  </si>
+  <si>
+    <t>3,366 (1,933-5,656)</t>
+  </si>
+  <si>
+    <t>3,422 (1,865-5,848)</t>
+  </si>
+  <si>
+    <t>8,632 (6,555-11,638)</t>
+  </si>
+  <si>
+    <t>14,155 (11,093-19,085)</t>
+  </si>
+  <si>
+    <t>19,406 (15,203-26,748)</t>
   </si>
   <si>
     <t>nan (0.0-0.0)</t>
   </si>
   <si>
-    <t>26.3 (14.4-80.0)</t>
-  </si>
-  <si>
-    <t>34.9 (16.6-90.8)</t>
-  </si>
-  <si>
-    <t>40.8 (18.9-102)</t>
-  </si>
-  <si>
-    <t>25.8 (12.9-77.4)</t>
-  </si>
-  <si>
-    <t>30.5 (14.4-87.4)</t>
-  </si>
-  <si>
-    <t>33.5 (16.0-98.2)</t>
-  </si>
-  <si>
-    <t>11.5 (5.7-29.3)</t>
-  </si>
-  <si>
-    <t>13.0 (6.4-33.2)</t>
-  </si>
-  <si>
-    <t>14.3 (7.1-36.8)</t>
-  </si>
-  <si>
-    <t>11.0 (5.4-29.0)</t>
-  </si>
-  <si>
-    <t>12.3 (5.9-32.8)</t>
-  </si>
-  <si>
-    <t>13.7 (6.6-36.7)</t>
-  </si>
-  <si>
-    <t>134.7 (66.5-482)</t>
-  </si>
-  <si>
-    <t>171.4 (76.1-586)</t>
-  </si>
-  <si>
-    <t>187.0 (87.2-677)</t>
-  </si>
-  <si>
-    <t>54.5 (25.0-123)</t>
-  </si>
-  <si>
-    <t>56.8 (26.0-132)</t>
-  </si>
-  <si>
-    <t>59.4 (26.5-138)</t>
-  </si>
-  <si>
-    <t>118.3 (60.3-343)</t>
-  </si>
-  <si>
-    <t>142.8 (68.3-395)</t>
-  </si>
-  <si>
-    <t>158.6 (75.4-454)</t>
-  </si>
-  <si>
-    <t>51.3 (23.3-117)</t>
-  </si>
-  <si>
-    <t>53.7 (24.1-126)</t>
-  </si>
-  <si>
-    <t>56.1 (24.9-133)</t>
-  </si>
-  <si>
-    <t>17.4 (8.3-48.6)</t>
-  </si>
-  <si>
-    <t>17.7 (8.5-53.9)</t>
-  </si>
-  <si>
-    <t>19.2 (9.0-59.3)</t>
-  </si>
-  <si>
-    <t>2.5 (1.2-6.8)</t>
-  </si>
-  <si>
-    <t>1.5 (0.7-4.2)</t>
-  </si>
-  <si>
-    <t>1.2 (0.5-3.3)</t>
-  </si>
-  <si>
-    <t>6.2 (3.0-16.9)</t>
-  </si>
-  <si>
-    <t>5.8 (2.7-15.7)</t>
-  </si>
-  <si>
-    <t>5.9 (2.7-16.5)</t>
-  </si>
-  <si>
-    <t>4.2 (2.0-10.4)</t>
-  </si>
-  <si>
-    <t>4.3 (2.0-10.5)</t>
-  </si>
-  <si>
-    <t>4.3 (2.0-10.7)</t>
-  </si>
-  <si>
-    <t>14.4 (5.8-37.6)</t>
-  </si>
-  <si>
-    <t>8.2 (3.4-22.6)</t>
-  </si>
-  <si>
-    <t>5.9 (2.4-16.9)</t>
-  </si>
-  <si>
-    <t>6.3 (3.0-14.7)</t>
-  </si>
-  <si>
-    <t>5.2 (2.5-12.4)</t>
-  </si>
-  <si>
-    <t>4.9 (2.2-11.8)</t>
+    <t>28.3 (14.5-75.8)</t>
+  </si>
+  <si>
+    <t>33.3 (16.5-85.0)</t>
+  </si>
+  <si>
+    <t>38.4 (18.5-94.4)</t>
+  </si>
+  <si>
+    <t>26.6 (13.6-73.0)</t>
+  </si>
+  <si>
+    <t>31.1 (15.1-82.9)</t>
+  </si>
+  <si>
+    <t>34.3 (16.5-91.1)</t>
+  </si>
+  <si>
+    <t>11.2 (6.5-25.2)</t>
+  </si>
+  <si>
+    <t>13.2 (7.4-28.6)</t>
+  </si>
+  <si>
+    <t>14.7 (8.3-32.7)</t>
+  </si>
+  <si>
+    <t>10.9 (6.4-25.1)</t>
+  </si>
+  <si>
+    <t>12.9 (7.3-28.4)</t>
+  </si>
+  <si>
+    <t>14.4 (8.1-32.2)</t>
+  </si>
+  <si>
+    <t>129.9 (66.4-426)</t>
+  </si>
+  <si>
+    <t>151.3 (75.6-515)</t>
+  </si>
+  <si>
+    <t>166.2 (84.2-605)</t>
+  </si>
+  <si>
+    <t>60.7 (32.7-137)</t>
+  </si>
+  <si>
+    <t>65.8 (34.4-145)</t>
+  </si>
+  <si>
+    <t>69.0 (36.1-152)</t>
+  </si>
+  <si>
+    <t>118.7 (61.4-355)</t>
+  </si>
+  <si>
+    <t>139.2 (68.2-417)</t>
+  </si>
+  <si>
+    <t>150.5 (76.0-479)</t>
+  </si>
+  <si>
+    <t>58.1 (31.4-130)</t>
+  </si>
+  <si>
+    <t>62.9 (32.8-138)</t>
+  </si>
+  <si>
+    <t>66.3 (34.2-144)</t>
+  </si>
+  <si>
+    <t>18.5 (9.5-42.4)</t>
+  </si>
+  <si>
+    <t>19.3 (10.4-47.7)</t>
+  </si>
+  <si>
+    <t>21.1 (11.1-52.7)</t>
+  </si>
+  <si>
+    <t>2.4 (1.2-5.6)</t>
+  </si>
+  <si>
+    <t>1.4 (0.7-3.4)</t>
+  </si>
+  <si>
+    <t>1.1 (0.5-2.7)</t>
+  </si>
+  <si>
+    <t>6.3 (3.6-14.0)</t>
+  </si>
+  <si>
+    <t>5.9 (3.4-12.8)</t>
+  </si>
+  <si>
+    <t>6.2 (3.5-13.1)</t>
+  </si>
+  <si>
+    <t>5.8 (3.1-11.7)</t>
+  </si>
+  <si>
+    <t>5.8 (3.2-11.9)</t>
+  </si>
+  <si>
+    <t>5.8 (3.2-12.0)</t>
+  </si>
+  <si>
+    <t>21.7 (9.2-48.1)</t>
+  </si>
+  <si>
+    <t>12.1 (5.3-28.6)</t>
+  </si>
+  <si>
+    <t>8.7 (3.9-21.5)</t>
+  </si>
+  <si>
+    <t>8.3 (4.6-16.4)</t>
+  </si>
+  <si>
+    <t>7.1 (3.8-14.0)</t>
+  </si>
+  <si>
+    <t>6.7 (3.6-13.4)</t>
   </si>
 </sst>
 </file>
